--- a/data/trans_dic/P15D$ingresado-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 38,42</t>
+          <t>7,23; 40,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 25,25</t>
+          <t>7,11; 24,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 25,78</t>
+          <t>5,6; 24,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 43,64</t>
+          <t>17,69; 45,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 20,37</t>
+          <t>2,45; 20,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 17,39</t>
+          <t>5,82; 18,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 20,2</t>
+          <t>4,63; 20,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 21,34</t>
+          <t>9,94; 22,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 22,12</t>
+          <t>6,17; 23,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,5</t>
+          <t>7,84; 18,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 18,81</t>
+          <t>7,24; 18,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 26,51</t>
+          <t>13,84; 25,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 19,12</t>
+          <t>4,92; 20,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 12,36</t>
+          <t>3,57; 11,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,46</t>
+          <t>4,22; 14,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 18,31</t>
+          <t>7,55; 18,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,58</t>
+          <t>0,0; 14,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,21</t>
+          <t>2,91; 12,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 17,9</t>
+          <t>2,73; 16,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 20,15</t>
+          <t>5,85; 20,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,8</t>
+          <t>3,44; 14,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,31</t>
+          <t>4,32; 10,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 12,93</t>
+          <t>4,97; 13,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 16,99</t>
+          <t>7,75; 16,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 48,01</t>
+          <t>5,65; 47,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 38,88</t>
+          <t>5,28; 37,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 44,16</t>
+          <t>3,37; 43,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 18,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 42,57</t>
+          <t>7,09; 39,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 14,99</t>
+          <t>1,57; 16,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 30,84</t>
+          <t>3,3; 31,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 10,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 32,73</t>
+          <t>9,27; 32,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 27,14</t>
+          <t>4,35; 28,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 21,8</t>
+          <t>8,34; 22,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,37</t>
+          <t>5,3; 12,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 17,12</t>
+          <t>7,27; 17,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 23,58</t>
+          <t>11,81; 22,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,86</t>
+          <t>1,89; 12,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,83</t>
+          <t>4,92; 12,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,52</t>
+          <t>6,48; 16,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,86</t>
+          <t>7,84; 16,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,32</t>
+          <t>6,68; 15,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,48</t>
+          <t>5,97; 10,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,76</t>
+          <t>7,63; 14,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 17,44</t>
+          <t>10,74; 17,59</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1830; 9673</t>
+          <t>1821; 10111</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5316; 18891</t>
+          <t>5315; 18514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2755; 11782</t>
+          <t>2558; 11156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5895; 15539</t>
+          <t>6298; 16300</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1115; 9273</t>
+          <t>1116; 9347</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6455; 19454</t>
+          <t>6507; 20548</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3451; 15070</t>
+          <t>3457; 15306</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7945; 16978</t>
+          <t>7907; 17910</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4693; 15642</t>
+          <t>4362; 16424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13942; 32670</t>
+          <t>14639; 34405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8037; 22634</t>
+          <t>8705; 22660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15831; 30524</t>
+          <t>15938; 29779</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3865; 15011</t>
+          <t>3864; 15834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6752; 22493</t>
+          <t>6497; 20506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4891; 16309</t>
+          <t>5120; 17860</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9493; 23809</t>
+          <t>9817; 23995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4760</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3141; 13878</t>
+          <t>3310; 14269</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2637; 15153</t>
+          <t>2310; 14063</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5474; 20541</t>
+          <t>5964; 21293</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4159; 17940</t>
+          <t>3910; 16341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12212; 30489</t>
+          <t>12779; 30372</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10407; 26613</t>
+          <t>10234; 27312</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18293; 39417</t>
+          <t>17989; 39356</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1099; 9315</t>
+          <t>1096; 9271</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1908</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1631; 11974</t>
+          <t>1626; 11421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1488; 14672</t>
+          <t>1119; 14407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5311</t>
+          <t>0; 5344</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2368; 13201</t>
+          <t>2197; 12224</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>470; 4627</t>
+          <t>483; 4993</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1055; 10066</t>
+          <t>1078; 10437</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5871</t>
+          <t>0; 6005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5803; 20229</t>
+          <t>5729; 19884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2755; 17392</t>
+          <t>2786; 17952</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10199; 26830</t>
+          <t>10271; 27270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15167; 34994</t>
+          <t>14998; 34495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14433; 33843</t>
+          <t>14362; 33905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22325; 46888</t>
+          <t>23485; 44721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1180; 10186</t>
+          <t>1777; 11797</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12527; 30078</t>
+          <t>12509; 31099</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12554; 31425</t>
+          <t>12332; 30864</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16635; 33683</t>
+          <t>16641; 34230</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13786; 33224</t>
+          <t>14495; 33396</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29418; 56293</t>
+          <t>32094; 57911</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31692; 57267</t>
+          <t>29600; 56523</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43595; 71729</t>
+          <t>44150; 72333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$ingresado-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 40,16</t>
+          <t>7,37; 39,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 24,75</t>
+          <t>7,55; 24,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 24,41</t>
+          <t>5,83; 24,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 45,78</t>
+          <t>15,21; 43,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 20,53</t>
+          <t>2,51; 19,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,37</t>
+          <t>5,62; 18,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 20,52</t>
+          <t>4,49; 20,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 22,51</t>
+          <t>10,34; 22,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 23,23</t>
+          <t>6,65; 23,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 18,43</t>
+          <t>7,82; 17,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 18,84</t>
+          <t>6,98; 18,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,84; 25,86</t>
+          <t>14,28; 26,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 20,17</t>
+          <t>4,94; 21,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,27</t>
+          <t>3,65; 11,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,74</t>
+          <t>4,02; 14,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 18,45</t>
+          <t>7,63; 18,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,9</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,55</t>
+          <t>2,74; 12,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 16,61</t>
+          <t>3,47; 16,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 20,88</t>
+          <t>5,92; 20,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 14,39</t>
+          <t>3,75; 15,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,27</t>
+          <t>4,34; 10,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,27</t>
+          <t>4,9; 13,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 16,96</t>
+          <t>8,32; 16,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 47,79</t>
+          <t>5,49; 51,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 37,09</t>
+          <t>5,6; 40,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 43,36</t>
+          <t>4,15; 43,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,57</t>
+          <t>0,0; 18,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 39,42</t>
+          <t>7,35; 41,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 16,18</t>
+          <t>1,44; 15,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 31,98</t>
+          <t>3,26; 29,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,95</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 32,17</t>
+          <t>9,28; 32,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 28,01</t>
+          <t>4,87; 29,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,16</t>
+          <t>7,97; 22,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,19</t>
+          <t>5,29; 12,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 17,15</t>
+          <t>7,24; 16,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 22,49</t>
+          <t>11,68; 23,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,58</t>
+          <t>2,01; 11,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,23</t>
+          <t>5,32; 12,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,22</t>
+          <t>6,92; 16,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 16,12</t>
+          <t>8,27; 16,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,4</t>
+          <t>6,56; 15,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,78</t>
+          <t>6,04; 10,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 14,57</t>
+          <t>8,31; 14,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 17,59</t>
+          <t>10,9; 17,88</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>23803</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1821; 10111</t>
+          <t>1855; 9905</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5315; 18514</t>
+          <t>5649; 18299</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2558; 11156</t>
+          <t>2665; 11289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6298; 16300</t>
+          <t>5755; 16334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1116; 9347</t>
+          <t>1143; 8910</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6507; 20548</t>
+          <t>6292; 20789</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3457; 15306</t>
+          <t>3351; 15301</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7907; 17910</t>
+          <t>8741; 18686</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4362; 16424</t>
+          <t>4701; 16371</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14639; 34405</t>
+          <t>14598; 33513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8705; 22660</t>
+          <t>8394; 22352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15938; 29779</t>
+          <t>17469; 32468</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>29242</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3864; 15834</t>
+          <t>3876; 16867</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6497; 20506</t>
+          <t>6651; 21106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5120; 17860</t>
+          <t>4877; 17231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9817; 23995</t>
+          <t>10694; 26309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5221</t>
+          <t>0; 5140</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3310; 14269</t>
+          <t>3110; 14264</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2310; 14063</t>
+          <t>2939; 13819</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5964; 21293</t>
+          <t>6567; 23179</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3910; 16341</t>
+          <t>4258; 17169</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12779; 30372</t>
+          <t>12831; 30207</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10234; 27312</t>
+          <t>10086; 27082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17989; 39356</t>
+          <t>20893; 41645</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>9868</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1096; 9271</t>
+          <t>1066; 9992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1626; 11421</t>
+          <t>1724; 12325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1119; 14407</t>
+          <t>1731; 18048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,37 +1945,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5344</t>
+          <t>0; 5439</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2197; 12224</t>
+          <t>2279; 12878</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>483; 4993</t>
+          <t>506; 5608</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1078; 10437</t>
+          <t>1063; 9654</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6005</t>
+          <t>0; 5060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5729; 19884</t>
+          <t>5734; 20081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2786; 17952</t>
+          <t>3742; 22771</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>62913</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10271; 27270</t>
+          <t>9806; 27330</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14998; 34495</t>
+          <t>14955; 34076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14362; 33905</t>
+          <t>14320; 32815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23485; 44721</t>
+          <t>25669; 51041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1777; 11797</t>
+          <t>1882; 10619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12509; 31099</t>
+          <t>13537; 30608</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12332; 30864</t>
+          <t>13168; 32182</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16641; 34230</t>
+          <t>19079; 39077</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14495; 33396</t>
+          <t>14220; 33122</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32094; 57911</t>
+          <t>32464; 58627</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29600; 56523</t>
+          <t>32228; 57675</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44150; 72333</t>
+          <t>49110; 80565</t>
         </is>
       </c>
     </row>
